--- a/artfynd/A 33644-2024 artfynd.xlsx
+++ b/artfynd/A 33644-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120845462</v>
+        <v>120845414</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>82385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617405</v>
+        <v>617288</v>
       </c>
       <c r="R2" t="n">
-        <v>7281304</v>
+        <v>7281368</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120845441</v>
+        <v>120845389</v>
       </c>
       <c r="B3" t="n">
-        <v>57501</v>
+        <v>78246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617378</v>
+        <v>617264</v>
       </c>
       <c r="R3" t="n">
-        <v>7281309</v>
+        <v>7281421</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,7 +890,7 @@
         <v>120845330</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120845414</v>
+        <v>120845462</v>
       </c>
       <c r="B5" t="n">
-        <v>82382</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617288</v>
+        <v>617405</v>
       </c>
       <c r="R5" t="n">
-        <v>7281368</v>
+        <v>7281304</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120845457</v>
+        <v>120845441</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,31 +1115,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617405</v>
+        <v>617378</v>
       </c>
       <c r="R6" t="n">
-        <v>7281304</v>
+        <v>7281309</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1187,11 +1183,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1212,7 @@
         <v>120845366</v>
       </c>
       <c r="B7" t="n">
-        <v>78243</v>
+        <v>78246</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120845389</v>
+        <v>120845457</v>
       </c>
       <c r="B8" t="n">
-        <v>78243</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,26 +1331,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>617264</v>
+        <v>617405</v>
       </c>
       <c r="R8" t="n">
-        <v>7281421</v>
+        <v>7281304</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1405,13 +1401,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1433,7 +1433,7 @@
         <v>120845383</v>
       </c>
       <c r="B9" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>121152599</v>
       </c>
       <c r="B10" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 33644-2024 artfynd.xlsx
+++ b/artfynd/A 33644-2024 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>121152599</v>
       </c>
       <c r="B10" t="n">
-        <v>82385</v>
+        <v>82388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 33644-2024 artfynd.xlsx
+++ b/artfynd/A 33644-2024 artfynd.xlsx
@@ -1539,7 +1539,7 @@
         <v>121152599</v>
       </c>
       <c r="B10" t="n">
-        <v>82388</v>
+        <v>82391</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
